--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487878_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487878_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5877</v>
+        <v>6.3975</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8223</v>
+        <v>5.1018</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7654</v>
+        <v>1.2957</v>
       </c>
       <c r="G2" t="n">
         <v>6.769</v>
@@ -610,13 +610,13 @@
         <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8364</v>
+        <v>0.6462</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2643</v>
+        <v>0.0153</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1007</v>
+        <v>0.631</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6015</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6482</v>
+        <v>5.4151</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1122</v>
+        <v>2.8204</v>
       </c>
       <c r="F3" t="n">
-        <v>2.536</v>
+        <v>2.5947</v>
       </c>
       <c r="G3" t="n">
         <v>8.053699999999999</v>
@@ -688,13 +688,13 @@
         <v>1.2487</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9081</v>
+        <v>-0.1412</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0.121</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3209</v>
+        <v>-0.2622</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0974</v>
+        <v>3.8221</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0811</v>
+        <v>2.7178</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0162</v>
+        <v>1.1043</v>
       </c>
       <c r="G4" t="n">
         <v>3.178</v>
@@ -766,13 +766,13 @@
         <v>1.0406</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0869</v>
+        <v>0.8116</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7763</v>
+        <v>0.4129</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3106</v>
+        <v>0.3987</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5838</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. VAN DER HEIJDEN</t>
+          <t>M. DENG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2255</v>
+        <v>1.6605</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3643</v>
+        <v>0.3072</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.1387</v>
+        <v>1.3533</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5664</v>
+        <v>1.6472</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5865</v>
+        <v>-1.4837</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9798</v>
+        <v>3.131</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9546</v>
+        <v>1.9211</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7993</v>
+        <v>-0.3158</v>
       </c>
       <c r="L5" t="n">
-        <v>2.1554</v>
+        <v>2.237</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3883</v>
+        <v>-0.2739</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2127</v>
+        <v>-1.1679</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1755</v>
+        <v>0.894</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2487</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.6244</v>
+        <v>-1.4568</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8731</v>
+        <v>1.4568</v>
       </c>
       <c r="S5" t="n">
-        <v>1.143</v>
+        <v>0.0132</v>
       </c>
       <c r="T5" t="n">
-        <v>1.034</v>
+        <v>-0.1571</v>
       </c>
       <c r="U5" t="n">
-        <v>0.109</v>
+        <v>0.1703</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.7325</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.7325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. DENG</t>
+          <t>D. HAYMAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1064</v>
+        <v>0.7834</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1348</v>
+        <v>1.2964</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9716</v>
+        <v>-0.5131</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6472</v>
+        <v>1.2708</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4837</v>
+        <v>0.0469</v>
       </c>
       <c r="I6" t="n">
-        <v>3.131</v>
+        <v>1.2238</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9211</v>
+        <v>1.4955</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3158</v>
+        <v>0.2022</v>
       </c>
       <c r="L6" t="n">
-        <v>2.237</v>
+        <v>1.2932</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2739</v>
+        <v>-0.2247</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1679</v>
+        <v>-0.1553</v>
       </c>
       <c r="O6" t="n">
-        <v>0.894</v>
+        <v>-0.0694</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.2487</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.4568</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5409</v>
+        <v>-0.3386</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3295</v>
+        <v>-0.199</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2113</v>
+        <v>-0.1396</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.3975</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. HAYMAN</t>
+          <t>E. VAN DER HEIJDEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4311</v>
+        <v>0.4335</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2964</v>
+        <v>3.5723</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8653999999999999</v>
+        <v>-3.1387</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2708</v>
+        <v>2.5664</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0469</v>
+        <v>0.5865</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2238</v>
+        <v>1.9798</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4955</v>
+        <v>3.9546</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2022</v>
+        <v>1.7993</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2932</v>
+        <v>2.1554</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2247</v>
+        <v>-1.3883</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1553</v>
+        <v>-1.2127</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0694</v>
+        <v>-0.1755</v>
       </c>
       <c r="P7" t="n">
         <v>1.2487</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.6244</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2487</v>
+        <v>1.8731</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6909</v>
+        <v>0.351</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.199</v>
+        <v>0.242</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4919</v>
+        <v>0.109</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3975</v>
+        <v>-3.7325</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3975</v>
+        <v>-3.7325</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. LLAMAS MARTINEZ</t>
+          <t>G. MCKAY JR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1681</v>
+        <v>-0.1177</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.01</v>
+        <v>0.1806</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8419</v>
+        <v>-0.2982</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6452</v>
+        <v>0.3784</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2623</v>
+        <v>0.0534</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3829</v>
+        <v>0.3249</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.0286</v>
+        <v>0.0968</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.107</v>
+        <v>0.0576</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0784</v>
+        <v>0.0392</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6166</v>
+        <v>0.2816</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1553</v>
+        <v>-0.0041</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4613</v>
+        <v>0.2857</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2487</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4568</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2284</v>
+        <v>0.0877</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0033</v>
+        <v>0.0838</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2317</v>
+        <v>0.0039</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
       <c r="W8" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.23</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. MCKAY JR</t>
+          <t>R. LLAMAS MARTINEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4201</v>
+        <v>-0.4221</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0337</v>
+        <v>-1.1172</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3863</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3784</v>
+        <v>-1.6452</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0534</v>
+        <v>-1.2623</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3249</v>
+        <v>-0.3829</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0968</v>
+        <v>-1.0286</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0576</v>
+        <v>-1.107</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0392</v>
+        <v>0.0784</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2816</v>
+        <v>-0.6166</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0041</v>
+        <v>-0.1553</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2857</v>
+        <v>-0.4613</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.2487</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.4568</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2146</v>
+        <v>-0.0256</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1305</v>
+        <v>-0.1105</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0842</v>
+        <v>0.0849</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5838</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-0.9423</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8137</v>
+        <v>-0.7065</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.089</v>
+        <v>-0.2358</v>
       </c>
       <c r="G10" t="n">
         <v>3.1584</v>
@@ -1234,13 +1234,13 @@
         <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1474</v>
+        <v>-0.1871</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8482</v>
+        <v>-0.741</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7007</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5838</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. AMADASUN</t>
+          <t>D. BULTO CASTILLO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3738</v>
+        <v>-2.6346</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3126</v>
+        <v>-0.4829</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0612</v>
+        <v>-2.1517</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3588</v>
+        <v>-2.0184</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.6952</v>
+        <v>-2.0298</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3364</v>
+        <v>0.0114</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.0483</v>
+        <v>-0.5201</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.2051</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1568</v>
+        <v>0.1176</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3105</v>
+        <v>-1.4983</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4901</v>
+        <v>-1.3922</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1796</v>
+        <v>-0.1061</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0.4162</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6093</v>
+        <v>0.135</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7763</v>
+        <v>0.0372</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.167</v>
+        <v>0.0979</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. BULTO CASTILLO</t>
+          <t>M. AMADASUN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.122</v>
+        <v>-3.1136</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9115</v>
+        <v>-3.1699</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2105</v>
+        <v>0.0562</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0184</v>
+        <v>-2.3588</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.0298</v>
+        <v>-2.6952</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0114</v>
+        <v>0.3364</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5201</v>
+        <v>-2.0483</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-2.2051</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1176</v>
+        <v>0.1568</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4983</v>
+        <v>-0.3105</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3922</v>
+        <v>-0.4901</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1061</v>
+        <v>0.1796</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4162</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R12" t="n">
         <v>0.4162</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3523</v>
+        <v>-0.1305</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3915</v>
+        <v>-0.0809</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0391</v>
+        <v>-0.0496</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.4634</v>
+        <v>-4.3093</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.009</v>
+        <v>-3.4732</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4544</v>
+        <v>-0.8361</v>
       </c>
       <c r="G13" t="n">
         <v>-0.9567</v>
@@ -1468,13 +1468,13 @@
         <v>1.4568</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.133</v>
+        <v>0.0211</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7829</v>
+        <v>-0.2471</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6499</v>
+        <v>0.2682</v>
       </c>
       <c r="V13" t="n">
         <v>-0.4599</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.646200000000004</v>
+        <v>6.972500000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>6.720599999999997</v>
+        <v>7.046799999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.07439999999999969</v>
+        <v>-0.07429999999999948</v>
       </c>
       <c r="G14" t="n">
         <v>20.0428</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9802999999999991</v>
+        <v>-0.9802999999999995</v>
       </c>
       <c r="I14" t="n">
         <v>21.0228</v>
@@ -1522,7 +1522,7 @@
         <v>23.2906</v>
       </c>
       <c r="K14" t="n">
-        <v>3.717099999999999</v>
+        <v>3.717100000000001</v>
       </c>
       <c r="L14" t="n">
         <v>19.5737</v>
@@ -1546,10 +1546,10 @@
         <v>12.487</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9167999999999998</v>
+        <v>1.2428</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9498</v>
+        <v>-0.6234</v>
       </c>
       <c r="U14" t="n">
         <v>1.8664</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8296</v>
+        <v>2.6829</v>
       </c>
       <c r="E15" t="n">
         <v>1.1225</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7072</v>
+        <v>1.5604</v>
       </c>
       <c r="G15" t="n">
         <v>0.2257</v>
@@ -1624,13 +1624,13 @@
         <v>2.0812</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1879</v>
+        <v>-0.3347</v>
       </c>
       <c r="T15" t="n">
         <v>-0.5624</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3745</v>
+        <v>0.2277</v>
       </c>
       <c r="V15" t="n">
         <v>1.7513</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7036</v>
+        <v>2.5623</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9204</v>
+        <v>3.4561</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2168</v>
+        <v>-0.8938</v>
       </c>
       <c r="G16" t="n">
         <v>0.3358</v>
@@ -1702,13 +1702,13 @@
         <v>2.4974</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3596</v>
+        <v>-0.5009</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0067</v>
+        <v>-0.4709</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3529</v>
+        <v>-0.0299</v>
       </c>
       <c r="V16" t="n">
         <v>0.23</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. ARQUES LOPEZ</t>
+          <t>P. ISERN MAZA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.143</v>
+        <v>2.031</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2442</v>
+        <v>2.8141</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1012</v>
+        <v>-0.7832</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7127</v>
+        <v>-1.7358</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1342</v>
+        <v>0.4473</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.8469</v>
+        <v>-2.1831</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3286</v>
+        <v>0.9423</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0037</v>
+        <v>0.9905</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6752</v>
+        <v>-0.0482</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0412</v>
+        <v>-2.6782</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1304</v>
+        <v>-0.5432</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.1717</v>
+        <v>-2.1349</v>
       </c>
       <c r="P17" t="n">
-        <v>1.2487</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6694</v>
+        <v>0.2205</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2519</v>
+        <v>-0.2395</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9212</v>
+        <v>0.46</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9376</v>
+        <v>3.9625</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1675</v>
+        <v>4.1925</v>
       </c>
       <c r="X17" t="n">
         <v>-0.23</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. ISERN MAZA</t>
+          <t>E. ARQUES LOPEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0563</v>
+        <v>1.1033</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9569</v>
+        <v>1.3514</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9006</v>
+        <v>-0.248</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7358</v>
+        <v>-1.7127</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4473</v>
+        <v>1.1342</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.1831</v>
+        <v>-2.8469</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9423</v>
+        <v>0.3286</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9905</v>
+        <v>1.0037</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0482</v>
+        <v>-0.6752</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6782</v>
+        <v>-2.0412</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5432</v>
+        <v>0.1304</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.1349</v>
+        <v>-2.1717</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7542</v>
+        <v>0.6297</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0967</v>
+        <v>-0.1447</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3426</v>
+        <v>0.7745</v>
       </c>
       <c r="V18" t="n">
-        <v>3.9625</v>
+        <v>0.9376</v>
       </c>
       <c r="W18" t="n">
-        <v>4.1925</v>
+        <v>1.1675</v>
       </c>
       <c r="X18" t="n">
         <v>-0.23</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7337</v>
+        <v>0.8305</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6062</v>
+        <v>2.8205</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8725</v>
+        <v>-1.99</v>
       </c>
       <c r="G19" t="n">
         <v>-1.3309</v>
@@ -1936,13 +1936,13 @@
         <v>1.4568</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4808</v>
+        <v>0.5777</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3171</v>
+        <v>-0.1028</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.6805</v>
       </c>
       <c r="V19" t="n">
         <v>1.1675</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. MARTIN MARTIN</t>
+          <t>I. ORDOÑEZ OCHOA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.265</v>
+        <v>-0.4765</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3119</v>
+        <v>-0.1964</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5768</v>
+        <v>-0.2801</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-4.2618</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3069</v>
+        <v>-1.1749</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.139</v>
+        <v>-3.0869</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6008</v>
+        <v>-0.8447</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3152</v>
+        <v>-0.2479</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7144</v>
+        <v>-0.5968</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4329</v>
+        <v>-3.4171</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0083</v>
+        <v>-0.927</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4247</v>
+        <v>-2.4901</v>
       </c>
       <c r="P20" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0406</v>
+        <v>2.7055</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6941000000000001</v>
+        <v>-0.3386</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7111</v>
+        <v>-0.2924</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0169</v>
+        <v>-0.0463</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1675</v>
+        <v>2.4589</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.9813</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1675</v>
+        <v>0.4776</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4052</v>
+        <v>-0.8147</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5685</v>
+        <v>0.2471</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9737</v>
+        <v>-1.0618</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6728</v>
@@ -2092,13 +2092,13 @@
         <v>0.4162</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4351</v>
+        <v>0.0256</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4534</v>
+        <v>0.1319</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0183</v>
+        <v>-0.1063</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5838</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. ORDOÑEZ OCHOA</t>
+          <t>P. MARTIN MARTIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.594</v>
+        <v>-1.0547</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1964</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3976</v>
+        <v>-1.7236</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.2618</v>
+        <v>-0.8322000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1749</v>
+        <v>1.3069</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.0869</v>
+        <v>-2.139</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8447</v>
+        <v>0.6008</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2479</v>
+        <v>1.3152</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5968</v>
+        <v>-0.7144</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.4171</v>
+        <v>-1.4329</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.927</v>
+        <v>-0.0083</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.4901</v>
+        <v>-1.4247</v>
       </c>
       <c r="P22" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7055</v>
+        <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.456</v>
+        <v>-0.0956</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2924</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U22" t="n">
         <v>-0.1637</v>
       </c>
       <c r="V22" t="n">
-        <v>2.4589</v>
+        <v>-1.1675</v>
       </c>
       <c r="W22" t="n">
-        <v>1.9813</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.4776</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.1005</v>
+        <v>-5.8671</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2116</v>
+        <v>-4.8901</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.889</v>
+        <v>-0.977</v>
       </c>
       <c r="G23" t="n">
         <v>-4.7807</v>
@@ -2248,13 +2248,13 @@
         <v>1.8731</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1117</v>
+        <v>-0.8783</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6277</v>
+        <v>-0.3062</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.484</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.7477</v>
+        <v>-7.6431</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.2482</v>
+        <v>-7.3197</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4995</v>
+        <v>-0.3234</v>
       </c>
       <c r="G24" t="n">
         <v>-5.2774</v>
@@ -2326,13 +2326,13 @@
         <v>2.7055</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6732</v>
+        <v>-0.2222</v>
       </c>
       <c r="T24" t="n">
-        <v>1.124</v>
+        <v>0.0524</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4508</v>
+        <v>-0.2746</v>
       </c>
       <c r="V24" t="n">
         <v>0.3538</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.6462</v>
+        <v>-6.646099999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>0.07439999999999891</v>
+        <v>0.07439999999999802</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.7205</v>
+        <v>-6.720500000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-20.0428</v>
@@ -2407,10 +2407,10 @@
         <v>-0.9167999999999998</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.8664</v>
+        <v>-1.8665</v>
       </c>
       <c r="U25" t="n">
-        <v>0.9496000000000001</v>
+        <v>0.9498</v>
       </c>
       <c r="V25" t="n">
         <v>9.110299999999999</v>
